--- a/data/trans_bre/P3A_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P3A_R-Estudios-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares en los que las tareas domésticas las realiza principalmente el/la entrevistado/a</t>
+          <t>Hogares en los que las tareas domésticas las realiza principalmente la persona entrevistada</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -612,42 +612,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>53,74</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>47,43</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>42,26</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>28,86</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>163,33%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>133,66%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>51,5%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>50,22; 56,91</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>43,51; 50,99</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>37,62; 46,65</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>24,69; 33,59</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>141,59; 187,65</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>113,97; 156,55</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>81,43; 118,89</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>42,07; 64,58</t>
         </is>
       </c>
     </row>
@@ -712,42 +712,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>50,85</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>39,65</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>35,22</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>34,8</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>156,4%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>87,86%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>65,57%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>58,82%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>47,57; 53,53</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>36,91; 42,32</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>32,64; 37,84</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>26,95; 53,07</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>137,61; 175,47</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>78,38; 97,82</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>58,49; 73,11</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>40,3; 128,4</t>
         </is>
       </c>
     </row>
@@ -812,42 +812,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>37,54</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>27,03</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>20,33</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>17,74</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>89,78%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>49,75%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>30,83%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>24,39%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>31,71; 43,23</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>20,43; 33,07</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>15,39; 25,42</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>12,99; 22,27</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>68,96; 112,45</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>35,34; 65,27</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>22,57; 41,05</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>17,13; 32,21</t>
         </is>
       </c>
     </row>
@@ -912,42 +912,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>49,87</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>39,96</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>34,15</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>30,22</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>145,82%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>91,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>64,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>49,34%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>47,7; 51,97</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>37,96; 42,21</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>32,08; 36,34</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>24,67; 42,91</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>133,71; 159,42</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>83,91; 100,01</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>58,53; 70,41</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>37,11; 87,7</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P3A_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P3A_R-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28,86</t>
+          <t>28,68</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>51,5%</t>
+          <t>50,93%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>50,22; 56,91</t>
+          <t>50,3; 57,03</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>43,51; 50,99</t>
+          <t>43,41; 50,97</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>37,62; 46,65</t>
+          <t>37,87; 46,42</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>24,69; 33,59</t>
+          <t>23,95; 32,87</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>141,59; 187,65</t>
+          <t>140,78; 186,97</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>113,97; 156,55</t>
+          <t>114,41; 155,77</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>81,43; 118,89</t>
+          <t>82,38; 117,65</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>42,07; 64,58</t>
+          <t>39,89; 62,7</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>34,8</t>
+          <t>27,4</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>58,82%</t>
+          <t>41,79%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>47,57; 53,53</t>
+          <t>48,03; 53,88</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>36,91; 42,32</t>
+          <t>36,82; 42,34</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>32,64; 37,84</t>
+          <t>32,5; 37,84</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26,95; 53,07</t>
+          <t>24,82; 30,32</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>137,61; 175,47</t>
+          <t>137,91; 176,06</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>78,38; 97,82</t>
+          <t>78,13; 98,86</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>58,49; 73,11</t>
+          <t>58,36; 73,3</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>40,3; 128,4</t>
+          <t>36,63; 48,0</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>17,74</t>
+          <t>17,91</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>24,76%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>31,71; 43,23</t>
+          <t>31,76; 43,23</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>20,43; 33,07</t>
+          <t>20,97; 33,34</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>15,39; 25,42</t>
+          <t>15,14; 25,24</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12,99; 22,27</t>
+          <t>13,81; 22,84</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>68,96; 112,45</t>
+          <t>70,19; 113,37</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>35,34; 65,27</t>
+          <t>35,83; 67,2</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>22,57; 41,05</t>
+          <t>21,77; 40,56</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>17,13; 32,21</t>
+          <t>18,52; 33,38</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>30,22</t>
+          <t>25,26</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>49,34%</t>
+          <t>38,61%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>47,7; 51,97</t>
+          <t>47,68; 52,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>37,96; 42,21</t>
+          <t>37,9; 42,19</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>32,08; 36,34</t>
+          <t>31,87; 36,14</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>24,67; 42,91</t>
+          <t>23,19; 27,47</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>133,71; 159,42</t>
+          <t>132,88; 159,32</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>83,91; 100,01</t>
+          <t>84,0; 99,89</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>58,53; 70,41</t>
+          <t>57,93; 69,77</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>37,11; 87,7</t>
+          <t>34,6; 43,19</t>
         </is>
       </c>
     </row>
